--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_LOCAL.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_LOCAL.xlsx
@@ -2375,11 +2375,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="92570915"/>
-        <c:axId val="43440905"/>
+        <c:axId val="11484266"/>
+        <c:axId val="5027649"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="92570915"/>
+        <c:axId val="11484266"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2413,7 +2413,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43440905"/>
+        <c:crossAx val="5027649"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2425,7 +2425,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="43440905"/>
+        <c:axId val="5027649"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2468,7 +2468,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92570915"/>
+        <c:crossAx val="11484266"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4307,11 +4307,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="41096831"/>
-        <c:axId val="81062652"/>
+        <c:axId val="84546056"/>
+        <c:axId val="34455810"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="41096831"/>
+        <c:axId val="84546056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4343,7 +4343,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81062652"/>
+        <c:crossAx val="34455810"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -4354,7 +4354,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="81062652"/>
+        <c:axId val="34455810"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="120"/>
@@ -4429,7 +4429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41096831"/>
+        <c:crossAx val="84546056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="AW20" s="33" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="33" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2973,$B$3:$B$2973)</f>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="AH22" s="22" t="n">
         <f aca="false">+S23/R23-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
@@ -8625,7 +8625,7 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="23" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="28" t="s">
         <v>27</v>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="S23" s="3" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="19"/>
       <c r="Y23" s="19"/>
@@ -9177,23 +9177,23 @@
       </c>
       <c r="AX29" s="43" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="43" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="43" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="43" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="43" t="n">
         <f aca="false">+AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="44"/>
       <c r="BD29" s="27"/>
@@ -13392,7 +13392,7 @@
       </c>
       <c r="AH86" s="61" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI86" s="61"/>
       <c r="AJ86" s="61"/>
@@ -13404,7 +13404,7 @@
       <c r="AP86" s="61"/>
       <c r="AQ86" s="61" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="87" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18999,15 +18999,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="25" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="19" t="n">
         <f aca="false">+D248*(1+C249)</f>
-        <v>99.3549590659784</v>
+        <v>100.779402443364</v>
       </c>
       <c r="F249" s="17" t="n">
         <v>46142</v>
@@ -19102,23 +19102,23 @@
       </c>
       <c r="T2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!BA29</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="X2" s="83" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="H39" s="98" t="n">
         <f aca="false">+'Datos ICP (2)'!AH86</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I39" s="98"/>
       <c r="J39" s="98"/>
@@ -20417,7 +20417,7 @@
       <c r="P39" s="98"/>
       <c r="Q39" s="98" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_LOCAL.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_LOCAL.xlsx
@@ -2375,11 +2375,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="11484266"/>
-        <c:axId val="5027649"/>
+        <c:axId val="54101733"/>
+        <c:axId val="64945977"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="11484266"/>
+        <c:axId val="54101733"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2413,7 +2413,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5027649"/>
+        <c:crossAx val="64945977"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2425,7 +2425,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="5027649"/>
+        <c:axId val="64945977"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2468,7 +2468,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11484266"/>
+        <c:crossAx val="54101733"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4307,11 +4307,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="84546056"/>
-        <c:axId val="34455810"/>
+        <c:axId val="74395628"/>
+        <c:axId val="80982063"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="84546056"/>
+        <c:axId val="74395628"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4343,7 +4343,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34455810"/>
+        <c:crossAx val="80982063"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -4354,7 +4354,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="34455810"/>
+        <c:axId val="80982063"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="120"/>
@@ -4429,7 +4429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84546056"/>
+        <c:crossAx val="74395628"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_LOCAL.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_LOCAL.xlsx
@@ -2375,11 +2375,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="54101733"/>
-        <c:axId val="64945977"/>
+        <c:axId val="52198064"/>
+        <c:axId val="27662090"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="54101733"/>
+        <c:axId val="52198064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2413,7 +2413,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64945977"/>
+        <c:crossAx val="27662090"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2425,7 +2425,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="64945977"/>
+        <c:axId val="27662090"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2468,7 +2468,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54101733"/>
+        <c:crossAx val="52198064"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4307,11 +4307,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="74395628"/>
-        <c:axId val="80982063"/>
+        <c:axId val="96872208"/>
+        <c:axId val="8641900"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="74395628"/>
+        <c:axId val="96872208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4343,7 +4343,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80982063"/>
+        <c:crossAx val="8641900"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -4354,7 +4354,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="80982063"/>
+        <c:axId val="8641900"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="120"/>
@@ -4429,7 +4429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74395628"/>
+        <c:crossAx val="96872208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_LOCAL.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_LOCAL.xlsx
@@ -2375,11 +2375,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="52198064"/>
-        <c:axId val="27662090"/>
+        <c:axId val="60720579"/>
+        <c:axId val="56290274"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="52198064"/>
+        <c:axId val="60720579"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2413,7 +2413,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27662090"/>
+        <c:crossAx val="56290274"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2425,7 +2425,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="27662090"/>
+        <c:axId val="56290274"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2468,7 +2468,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52198064"/>
+        <c:crossAx val="60720579"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4307,11 +4307,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="96872208"/>
-        <c:axId val="8641900"/>
+        <c:axId val="40363400"/>
+        <c:axId val="96127906"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="96872208"/>
+        <c:axId val="40363400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4343,7 +4343,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8641900"/>
+        <c:crossAx val="96127906"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -4354,7 +4354,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="8641900"/>
+        <c:axId val="96127906"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="120"/>
@@ -4429,7 +4429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96872208"/>
+        <c:crossAx val="40363400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
